--- a/03_Documentos_Tecnicos/PEB_Pausa_Maule_completado.xlsx
+++ b/03_Documentos_Tecnicos/PEB_Pausa_Maule_completado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/57b91da64fcc1594/Escritorio/CURSO BIM^MIA/PRACTICO/CLASE 7 SEPTIEMBRE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\claude\C--Users-user-OneDrive-Escritorio-CURSO-BIM-IA-Claude\63969694-b2af-4bd1-919d-9b63abdf2687\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_858E0603925EBA3FEC2844B64EA69E7EA47AB403" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{638F2765-FBB9-4370-BDD8-FE84BE30EA60}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8271F08F-EF8D-4164-A57E-C8E4523E4C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="4440" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BEP" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>MÉTODO TBC · THE BIM CO-WORK</t>
   </si>
@@ -145,9 +145,6 @@
     <t>NIVEL DE INFORMACIÓN (NDI) — DETALLE DEL ASPECTO 3</t>
   </si>
   <si>
-    <t>NDI 2 como base de anteproyecto, verificado en vivo contra el modelo Revit el 06-09-2026 y actualizado el 08-09-2026 tras el renombramiento de tipos/familias y la incorporacion de fichas tecnicas de Moldupanel, Arauco y Vidrios Lirquen. Tipo = informacion fija de la familia-tipo. Instancia = informacion propia de cada elemento colocado.</t>
-  </si>
-  <si>
     <t>NDI</t>
   </si>
   <si>
@@ -202,9 +199,6 @@
     <t>Paneles de muro cortina</t>
   </si>
   <si>
-    <t>PANEL_MADERA (x192). Familia de sistema System Panel. Material corregido 08-09-2026 de MT_VIDRIO (erroneo) a MT_PINO RADIATA: es un paramento solido de madera, NO vidrio. Se retiro la ficha de Vidrios Lirquen (no aplicaba).</t>
-  </si>
-  <si>
     <t>Dimension real del pano, posicion en la rejilla.</t>
   </si>
   <si>
@@ -226,9 +220,6 @@
     <t>Pilares estructurales</t>
   </si>
   <si>
-    <t>130X130 (x16). Familia: PILAR_Pino Radiata_Rectangular. Ficha Hilam MLE confirmada sin discrepancia (glulam estructural certificado NCh2148/NCh2165).</t>
-  </si>
-  <si>
     <t>Nivel base y superior, altura real, LoadBearing.</t>
   </si>
   <si>
@@ -238,9 +229,6 @@
     <t>Armazón estructural</t>
   </si>
   <si>
-    <t>2X8_PRINCIPAL (x8, 50x200mm) . 2X4_SECUNDARIA (x15, 50x100mm). Familia renombrada de 'M_Glulam-Western Species' a 'VIGA_Pino Radiata Dimensionada_Rectangular': CORRECCION 08-09-2026, no es glulam estructural sino madera dimensionada Arauco (MSD/Cepillado), material MT_PINO RADIATA. Discrepancia anterior resuelta.</t>
-  </si>
-  <si>
     <t>Longitud real, nivel, sistema de vigas al que pertenece, LoadBearing.</t>
   </si>
   <si>
@@ -277,19 +265,43 @@
     <t>No aplica: Rooms no tienen family type en Revit (TypeId = -1).</t>
   </si>
   <si>
-    <t>Nombre, Numero, Nivel, Area y Perimetro completos en las 9 habitaciones (incluye PASILLO #09, Nivel N1, 2.59 m2, agregada 08-09-2026). Departamento pendiente en las 9. Area total 79.45 m2.</t>
-  </si>
-  <si>
     <t>Analisis de programa espacial identifica con los primeros campos y contrasta el programa con los siguientes.</t>
   </si>
   <si>
-    <t>Categorías excluidas: Ventanas, muros interiores y puertas interiores no existen en el modelo. Los vanos se resuelven con seis muros cortina y la compartimentación con trece líneas de separación de habitación.</t>
-  </si>
-  <si>
     <t>Limitación conocida: los parámetros IFC de proyecto no están vinculados a las categorías de muro cortina. Exigir información alfanumérica normalizada en montantes, paneles y rejillas requiere ampliar antes esa vinculación.</t>
   </si>
   <si>
     <t>Hallazgo actualizado 08-09-2026: la familia de vigas fue renombrada de 'M_Glulam-Western Species' a 'VIGA_Pino Radiata Dimensionada_Rectangular' (resuelto). Montantes (Rectangular Mullion) y paneles (System Panel) siguen en ingles porque son familias de sistema de Revit: no se pueden renombrar (limitacion de la plataforma, no una tarea pendiente).</t>
+  </si>
+  <si>
+    <t>NDI 2 como base de anteproyecto, verificado en vivo contra el modelo Revit el 06-09-2026 y actualizado el 08-09-2026 tras el renombramiento de tipos/familias y la incorporacion de fichas tecnicas de Moldupanel, Arauco y Vidrios Lirquen. Tipo = informacion fija de la familia-tipo. Instancia = informacion propia de cada elemento colocado. Actualizado el 02-10-2026: se incorporo la categoria Cimentacion estructural (16 zapatas), se unifico el material del pilar a MT_PINO RADIATA, se corrigieron conteos (armazon 2X4 x16) y el nivel y departamento de las habitaciones.</t>
+  </si>
+  <si>
+    <t>Empty (x192). Familia de sistema System Panel (Empty System Panel). Sin material: celosia intencional, espacio libre entre los montantes de madera (decision de proyecto confirmada). Se retiro la ficha de Vidrios Lirquen (no aplicaba).</t>
+  </si>
+  <si>
+    <t>130X130 (x16). Familia: PILAR_Pino Radiata_Rectangular. Ficha Hilam MLE confirmada sin discrepancia (glulam estructural certificado NCh2148/NCh2165). Material en el modelo: MT_PINO RADIATA (unificado el 30-09-2026).</t>
+  </si>
+  <si>
+    <t>2X8_PRINCIPAL (x8, 50x200mm) . 2X4_SECUNDARIA (x16, 50x100mm). Familia renombrada de 'M_Glulam-Western Species' a 'VIGA_Pino Radiata Dimensionada_Rectangular': CORRECCION 08-09-2026, no es glulam estructural sino madera dimensionada Arauco (MSD/Cepillado), material MT_PINO RADIATA. Discrepancia anterior resuelta.</t>
+  </si>
+  <si>
+    <t>Nombre, Numero, Nivel, Area y Perimetro completos en las 9 habitaciones (incluye PASILLO #09, Nivel NPT, 2.59 m2, agregada 08-09-2026). Departamento completo en 8 de 9 (pendiente solo en PASILLO). Todas las habitaciones estan en nivel NPT. Area total 79.45 m2.</t>
+  </si>
+  <si>
+    <t>Categorías excluidas: Ventanas, muros interiores y puertas interiores no existen en el modelo. Los vanos se resuelven con seis muros cortina y la compartimentación con dieciocho líneas de separación de habitación.</t>
+  </si>
+  <si>
+    <t>Cimentación estructural</t>
+  </si>
+  <si>
+    <t>ZAPATA_Hormigon Armado_Aislada (x16, 60x60x50cm). Familia: Zapata. Material: MT_HORMIGON ARMADO (reasignado el 30-09-2026 desde el material generico de Revit). Ficha Melon (hormigon con fibra) como referencia: la resistencia 20/25/30 MPa es un rango, no un valor unico. Parametros NDI2 aun no vinculados a esta categoria.</t>
+  </si>
+  <si>
+    <t>Nivel NOG_FUNDACIONES (cota -0.20 m), posicion bajo cada pilar, Material estructural (a nivel de instancia).</t>
+  </si>
+  <si>
+    <t>Coordinacion 3D: cada zapata debe quedar bajo su pilar. Diseno de especialidades: la dimension 60x60x50 es de anteproyecto, pendiente de calculo geotecnico y estructural.</t>
   </si>
 </sst>
 </file>
@@ -532,32 +544,32 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -795,17 +807,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="4" width="46" customWidth="1"/>
-    <col min="5" max="5" width="40.7265625" customWidth="1"/>
+    <col min="5" max="5" width="40.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16"/>
@@ -813,8 +825,8 @@
       <c r="D1" s="16"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="25" t="s">
+    <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="16"/>
@@ -822,8 +834,8 @@
       <c r="D2" s="16"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="24" t="s">
+    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="16"/>
@@ -831,15 +843,15 @@
       <c r="D3" s="16"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="16"/>
@@ -847,80 +859,80 @@
       <c r="D5" s="16"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="19" t="s">
+    <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="17" t="s">
+      <c r="B6" s="19"/>
+      <c r="C6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="18"/>
+      <c r="D6" s="19"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="19" t="s">
+    <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="17" t="s">
+      <c r="B7" s="19"/>
+      <c r="C7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="18"/>
+      <c r="D7" s="19"/>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="19" t="s">
+    <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="17" t="s">
+      <c r="B8" s="19"/>
+      <c r="C8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="18"/>
+      <c r="D8" s="19"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="19" t="s">
+    <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="17" t="s">
+      <c r="B9" s="19"/>
+      <c r="C9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="18"/>
+      <c r="D9" s="19"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="19" t="s">
+    <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="17" t="s">
+      <c r="B10" s="19"/>
+      <c r="C10" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="18"/>
+      <c r="D10" s="19"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19" t="s">
+    <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="17" t="s">
+      <c r="B11" s="19"/>
+      <c r="C11" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="18"/>
+      <c r="D11" s="19"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
@@ -935,7 +947,7 @@
       </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5" ht="74.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>20</v>
       </c>
@@ -950,7 +962,7 @@
       </c>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:5" ht="74.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>24</v>
       </c>
@@ -965,7 +977,7 @@
       </c>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" ht="74.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>28</v>
       </c>
@@ -980,7 +992,7 @@
       </c>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" ht="74.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -995,7 +1007,7 @@
       </c>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" ht="74.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>36</v>
       </c>
@@ -1010,22 +1022,22 @@
       </c>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="21" t="s">
+    <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22" t="s">
         <v>40</v>
       </c>
       <c r="B21" s="16"/>
@@ -1033,239 +1045,248 @@
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
     </row>
-    <row r="22" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="23" t="s">
-        <v>41</v>
+    <row r="22" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="24" t="s">
+        <v>84</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
     </row>
-    <row r="24" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="D24" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="E24" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>2</v>
       </c>
       <c r="B25" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="D25" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="E25" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>2</v>
       </c>
       <c r="B26" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="D26" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="E26" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>2</v>
       </c>
       <c r="B27" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="D27" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="E27" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E27" s="13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>2</v>
       </c>
       <c r="B28" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="E28" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>2</v>
       </c>
       <c r="B29" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="E29" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>2</v>
       </c>
       <c r="B30" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:5" ht="102" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>2</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="102" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>2</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>2</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>2</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>84</v>
+        <v>75</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>76</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-    </row>
-    <row r="37" spans="1:5" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="11">
+        <v>2</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="13" t="s">
         <v>88</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="15" t="s">
+        <v>89</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
     </row>
-    <row r="38" spans="1:5" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="20" t="s">
-        <v>89</v>
+    <row r="38" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="15" t="s">
+        <v>82</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
     </row>
+    <row r="39" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+    </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="A8:B8"/>
@@ -1275,10 +1296,18 @@
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A36:E36"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A37:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="36" orientation="landscape" r:id="rId1"/>

--- a/03_Documentos_Tecnicos/PEB_Pausa_Maule_completado.xlsx
+++ b/03_Documentos_Tecnicos/PEB_Pausa_Maule_completado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\claude\C--Users-user-OneDrive-Escritorio-CURSO-BIM-IA-Claude\63969694-b2af-4bd1-919d-9b63abdf2687\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8271F08F-EF8D-4164-A57E-C8E4523E4C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA605CF3-0398-4CB8-9AEF-1FD7375BB5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -274,9 +274,6 @@
     <t>Hallazgo actualizado 08-09-2026: la familia de vigas fue renombrada de 'M_Glulam-Western Species' a 'VIGA_Pino Radiata Dimensionada_Rectangular' (resuelto). Montantes (Rectangular Mullion) y paneles (System Panel) siguen en ingles porque son familias de sistema de Revit: no se pueden renombrar (limitacion de la plataforma, no una tarea pendiente).</t>
   </si>
   <si>
-    <t>NDI 2 como base de anteproyecto, verificado en vivo contra el modelo Revit el 06-09-2026 y actualizado el 08-09-2026 tras el renombramiento de tipos/familias y la incorporacion de fichas tecnicas de Moldupanel, Arauco y Vidrios Lirquen. Tipo = informacion fija de la familia-tipo. Instancia = informacion propia de cada elemento colocado. Actualizado el 02-10-2026: se incorporo la categoria Cimentacion estructural (16 zapatas), se unifico el material del pilar a MT_PINO RADIATA, se corrigieron conteos (armazon 2X4 x16) y el nivel y departamento de las habitaciones.</t>
-  </si>
-  <si>
     <t>Empty (x192). Familia de sistema System Panel (Empty System Panel). Sin material: celosia intencional, espacio libre entre los montantes de madera (decision de proyecto confirmada). Se retiro la ficha de Vidrios Lirquen (no aplicaba).</t>
   </si>
   <si>
@@ -295,13 +292,16 @@
     <t>Cimentación estructural</t>
   </si>
   <si>
-    <t>ZAPATA_Hormigon Armado_Aislada (x16, 60x60x50cm). Familia: Zapata. Material: MT_HORMIGON ARMADO (reasignado el 30-09-2026 desde el material generico de Revit). Ficha Melon (hormigon con fibra) como referencia: la resistencia 20/25/30 MPa es un rango, no un valor unico. Parametros NDI2 aun no vinculados a esta categoria.</t>
-  </si>
-  <si>
     <t>Nivel NOG_FUNDACIONES (cota -0.20 m), posicion bajo cada pilar, Material estructural (a nivel de instancia).</t>
   </si>
   <si>
     <t>Coordinacion 3D: cada zapata debe quedar bajo su pilar. Diseno de especialidades: la dimension 60x60x50 es de anteproyecto, pendiente de calculo geotecnico y estructural.</t>
+  </si>
+  <si>
+    <t>ZAPATA_Hormigon Armado_Aislada (x16, 60x60x50cm). Familia: Zapata. Material: MT_HORMIGON ARMADO (reasignado el 30-09-2026 desde el material generico de Revit). Ficha Melon (hormigon con fibra) como referencia: la resistencia 20/25/30 MPa es un rango, no un valor unico. NDI2_Fuente_Ficha y NDI2_Observacion vinculados a esta categoria y con valores (02-10-2026).</t>
+  </si>
+  <si>
+    <t>NDI 2 como base de anteproyecto, verificado en vivo contra el modelo Revit el 06-09-2026 y actualizado el 08-09-2026 tras el renombramiento de tipos/familias y la incorporacion de fichas tecnicas de Moldupanel, Arauco y Vidrios Lirquen. Tipo = informacion fija de la familia-tipo. Instancia = informacion propia de cada elemento colocado. Actualizado el 02-10-2026: se incorporo la categoria Cimentacion estructural (16 zapatas, con parametros NDI2 vinculados), se unifico el material del pilar a MT_PINO RADIATA, se corrigieron conteos (armazon 2X4 x16) y el nivel y departamento de las habitaciones.</t>
   </si>
 </sst>
 </file>
@@ -544,31 +544,31 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -817,7 +817,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16"/>
@@ -826,7 +826,7 @@
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="16"/>
@@ -835,7 +835,7 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="16"/>
@@ -851,7 +851,7 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="21" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="16"/>
@@ -860,69 +860,69 @@
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="21" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="19"/>
+      <c r="D6" s="18"/>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="21" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="19"/>
+      <c r="D7" s="18"/>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="21" t="s">
+      <c r="B8" s="18"/>
+      <c r="C8" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="19"/>
+      <c r="D8" s="18"/>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="21" t="s">
+      <c r="B9" s="18"/>
+      <c r="C9" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="19"/>
+      <c r="D9" s="18"/>
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="21" t="s">
+      <c r="B10" s="18"/>
+      <c r="C10" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="19"/>
+      <c r="D10" s="18"/>
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="21" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="19"/>
+      <c r="D11" s="18"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1037,7 +1037,7 @@
       <c r="E20" s="1"/>
     </row>
     <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="25" t="s">
         <v>40</v>
       </c>
       <c r="B21" s="16"/>
@@ -1046,8 +1046,8 @@
       <c r="E21" s="16"/>
     </row>
     <row r="22" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
-        <v>84</v>
+      <c r="A22" s="20" t="s">
+        <v>93</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -1130,7 +1130,7 @@
         <v>58</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>59</v>
@@ -1164,7 +1164,7 @@
         <v>65</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>66</v>
@@ -1181,7 +1181,7 @@
         <v>68</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>69</v>
@@ -1190,21 +1190,21 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="102" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>2</v>
       </c>
       <c r="B32" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="E32" s="13" t="s">
         <v>91</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1252,15 +1252,15 @@
         <v>80</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E35" s="13" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
-        <v>89</v>
+      <c r="A37" s="22" t="s">
+        <v>88</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -1268,7 +1268,7 @@
       <c r="E37" s="16"/>
     </row>
     <row r="38" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="22" t="s">
         <v>82</v>
       </c>
       <c r="B38" s="16"/>
@@ -1277,7 +1277,7 @@
       <c r="E38" s="16"/>
     </row>
     <row r="39" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="22" t="s">
         <v>83</v>
       </c>
       <c r="B39" s="16"/>
@@ -1287,6 +1287,15 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A37:E37"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="A8:B8"/>
@@ -1299,15 +1308,6 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A37:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="36" orientation="landscape" r:id="rId1"/>

--- a/03_Documentos_Tecnicos/PEB_Pausa_Maule_completado.xlsx
+++ b/03_Documentos_Tecnicos/PEB_Pausa_Maule_completado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\claude\C--Users-user-OneDrive-Escritorio-CURSO-BIM-IA-Claude\63969694-b2af-4bd1-919d-9b63abdf2687\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA605CF3-0398-4CB8-9AEF-1FD7375BB5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612709D2-8710-4067-9FDA-FA69BC2125FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -166,12 +166,6 @@
     <t>MURO_EXT_QUINCHA_12cm (x11) . MURO_CORTINA_EXT_MADERA (x6). Familias: Muro basico / Muro cortina. Nivel tipo: espesor de capas y material (material real: MT_TIERRA_QUINCHA; ficha CONSTRUCCION_CON_QUINCHA_LIVIANA_1a_edicion.pdf).</t>
   </si>
   <si>
-    <t>Nivel base y superior, longitud real del tramo. IsExternal y LoadBearing viven en instancia (ambos vacios hoy).</t>
-  </si>
-  <si>
-    <t>Coordinacion 3D necesita espesor y posicion reales para el encuentro con pilares y cubierta. Diseno de especialidades usa LoadBearing para separar quincha portante de muro cortina.</t>
-  </si>
-  <si>
     <t>Rejillas de muro cortina</t>
   </si>
   <si>
@@ -220,18 +214,12 @@
     <t>Pilares estructurales</t>
   </si>
   <si>
-    <t>Nivel base y superior, altura real, LoadBearing.</t>
-  </si>
-  <si>
     <t>Coordinacion 3D: el pilar choca con muros y vigas. La seccion debe ser dato del tipo, no solo su nombre.</t>
   </si>
   <si>
     <t>Armazón estructural</t>
   </si>
   <si>
-    <t>Longitud real, nivel, sistema de vigas al que pertenece, LoadBearing.</t>
-  </si>
-  <si>
     <t>Revision del diseno comprueba la jerarquia entre principales y secundarias, ya resuelta en los tipos.</t>
   </si>
   <si>
@@ -302,6 +290,18 @@
   </si>
   <si>
     <t>NDI 2 como base de anteproyecto, verificado en vivo contra el modelo Revit el 06-09-2026 y actualizado el 08-09-2026 tras el renombramiento de tipos/familias y la incorporacion de fichas tecnicas de Moldupanel, Arauco y Vidrios Lirquen. Tipo = informacion fija de la familia-tipo. Instancia = informacion propia de cada elemento colocado. Actualizado el 02-10-2026: se incorporo la categoria Cimentacion estructural (16 zapatas, con parametros NDI2 vinculados), se unifico el material del pilar a MT_PINO RADIATA, se corrigieron conteos (armazon 2X4 x16) y el nivel y departamento de las habitaciones.</t>
+  </si>
+  <si>
+    <t>Nivel base y superior, longitud real del tramo. IsExternal = Si en los 17 muros (tipo e instancia, 02-10-2026); LoadBearing no esta vinculado a esta categoria.</t>
+  </si>
+  <si>
+    <t>Coordinacion 3D necesita espesor y posicion reales para el encuentro con pilares y cubierta. Diseno de especialidades usa IsExternal para separar muros de fachada de la compartimentacion.</t>
+  </si>
+  <si>
+    <t>Nivel base y superior, altura real. LoadBearing (de tipo) = 1.</t>
+  </si>
+  <si>
+    <t>Longitud real, nivel, sistema de vigas al que pertenece. LoadBearing (de tipo) = 1.</t>
   </si>
 </sst>
 </file>
@@ -544,31 +544,31 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -817,7 +817,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16"/>
@@ -826,7 +826,7 @@
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="16"/>
@@ -835,7 +835,7 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="16"/>
@@ -851,7 +851,7 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="25" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="16"/>
@@ -860,69 +860,69 @@
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="17" t="s">
+      <c r="B6" s="19"/>
+      <c r="C6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="18"/>
+      <c r="D6" s="19"/>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="17" t="s">
+      <c r="B7" s="19"/>
+      <c r="C7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="18"/>
+      <c r="D7" s="19"/>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="17" t="s">
+      <c r="B8" s="19"/>
+      <c r="C8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="18"/>
+      <c r="D8" s="19"/>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="17" t="s">
+      <c r="B9" s="19"/>
+      <c r="C9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="18"/>
+      <c r="D9" s="19"/>
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="17" t="s">
+      <c r="B10" s="19"/>
+      <c r="C10" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="18"/>
+      <c r="D10" s="19"/>
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="17" t="s">
+      <c r="B11" s="19"/>
+      <c r="C11" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="18"/>
+      <c r="D11" s="19"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1037,7 +1037,7 @@
       <c r="E20" s="1"/>
     </row>
     <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="22" t="s">
         <v>40</v>
       </c>
       <c r="B21" s="16"/>
@@ -1046,8 +1046,8 @@
       <c r="E21" s="16"/>
     </row>
     <row r="22" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
-        <v>93</v>
+      <c r="A22" s="24" t="s">
+        <v>89</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -1071,7 +1071,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>2</v>
       </c>
@@ -1082,10 +1082,10 @@
         <v>47</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1093,16 +1093,16 @@
         <v>2</v>
       </c>
       <c r="B26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="E26" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1110,16 +1110,16 @@
         <v>2</v>
       </c>
       <c r="B27" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="E27" s="13" t="s">
         <v>55</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
@@ -1127,16 +1127,16 @@
         <v>2</v>
       </c>
       <c r="B28" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="13" t="s">
         <v>58</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1144,16 +1144,16 @@
         <v>2</v>
       </c>
       <c r="B29" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="E29" s="13" t="s">
         <v>62</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
@@ -1161,16 +1161,16 @@
         <v>2</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="102" x14ac:dyDescent="0.25">
@@ -1178,16 +1178,16 @@
         <v>2</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="114.75" x14ac:dyDescent="0.25">
@@ -1195,16 +1195,16 @@
         <v>2</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1212,16 +1212,16 @@
         <v>2</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1229,16 +1229,16 @@
         <v>2</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
@@ -1246,21 +1246,21 @@
         <v>2</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="22" t="s">
-        <v>88</v>
+      <c r="A37" s="15" t="s">
+        <v>84</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -1268,8 +1268,8 @@
       <c r="E37" s="16"/>
     </row>
     <row r="38" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="22" t="s">
-        <v>82</v>
+      <c r="A38" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -1277,8 +1277,8 @@
       <c r="E38" s="16"/>
     </row>
     <row r="39" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="22" t="s">
-        <v>83</v>
+      <c r="A39" s="15" t="s">
+        <v>79</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -1287,15 +1287,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A37:E37"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="A8:B8"/>
@@ -1308,6 +1299,15 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A37:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="36" orientation="landscape" r:id="rId1"/>

--- a/03_Documentos_Tecnicos/PEB_Pausa_Maule_completado.xlsx
+++ b/03_Documentos_Tecnicos/PEB_Pausa_Maule_completado.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\claude\C--Users-user-OneDrive-Escritorio-CURSO-BIM-IA-Claude\63969694-b2af-4bd1-919d-9b63abdf2687\scratchpad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\claude\C--Users-user-OneDrive-Escritorio-CURSO-BIM-IA-Claude\c32490e3-48b8-4c11-9b04-e055733501a8\scratchpad\audit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612709D2-8710-4067-9FDA-FA69BC2125FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C3548C-49E1-4D0C-9488-917598F0AB7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BEP" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t>MÉTODO TBC · THE BIM CO-WORK</t>
   </si>
@@ -163,145 +163,181 @@
     <t>Muros</t>
   </si>
   <si>
-    <t>MURO_EXT_QUINCHA_12cm (x11) . MURO_CORTINA_EXT_MADERA (x6). Familias: Muro basico / Muro cortina. Nivel tipo: espesor de capas y material (material real: MT_TIERRA_QUINCHA; ficha CONSTRUCCION_CON_QUINCHA_LIVIANA_1a_edicion.pdf).</t>
-  </si>
-  <si>
     <t>Rejillas de muro cortina</t>
   </si>
   <si>
-    <t>No aplica: es una linea de rejilla (CurtainGridLine), no una familia con tipo propio.</t>
-  </si>
-  <si>
-    <t>Modulacion U/V, posicion en el muro, muro anfitrion.</t>
-  </si>
-  <si>
-    <t>Revision del diseno: la modulacion 2x16 es una decision de proyecto. Coordinacion 3D: gobierna donde caen montantes y paneles.</t>
-  </si>
-  <si>
     <t>Montantes de muro cortina</t>
   </si>
   <si>
-    <t>MADERA_1.25X10cm (x396). Familia de sistema: Rectangular Mullion (nombre de sistema Revit, no renombrable). Material: MT_PINO RADIATA. Ficha: Arauco Cepillado (agregada 08-09-2026).</t>
-  </si>
-  <si>
-    <t>Longitud real, posicion en la rejilla, resolucion en esquinas.</t>
-  </si>
-  <si>
-    <t>Coordinacion 3D: el montante perimetral choca con viga y pilar. Diseno de especialidades: es madera vista, su seccion forma parte del partido.</t>
-  </si>
-  <si>
     <t>Paneles de muro cortina</t>
   </si>
   <si>
-    <t>Dimension real del pano, posicion en la rejilla.</t>
-  </si>
-  <si>
-    <t>Revision del diseno: el pano resuelve la relacion interior-exterior que sustituye a las ventanas. Analisis de programa espacial: condiciona luz y vista.</t>
-  </si>
-  <si>
     <t>Puertas</t>
   </si>
   <si>
-    <t>80X210cm (x2). Familia: PRT_INT_SIMPLE_MADERA. Material corregido de TBC_PuertaMetalicaPintada (erroneo, contradecia el nombre madera) a TBC_Madera. Ficha: Moldupanel, Puerta Pino Radiata Italia 80x210cm (agregada 08-09-2026).</t>
-  </si>
-  <si>
-    <t>Muro anfitrion, sentido de apertura, Marca (6, 9), IsExternal.</t>
-  </si>
-  <si>
-    <t>Revision del diseno verifica ancho libre y sentido de apertura. IsExternal distinguiria acceso de interior.</t>
-  </si>
-  <si>
     <t>Pilares estructurales</t>
   </si>
   <si>
-    <t>Coordinacion 3D: el pilar choca con muros y vigas. La seccion debe ser dato del tipo, no solo su nombre.</t>
-  </si>
-  <si>
     <t>Armazón estructural</t>
   </si>
   <si>
-    <t>Revision del diseno comprueba la jerarquia entre principales y secundarias, ya resuelta en los tipos.</t>
-  </si>
-  <si>
     <t>Suelos</t>
   </si>
   <si>
-    <t>RADIER_INT_HA_15cm (x1) . RADIER_PULIDO_INT_HA_2cm (x1) [espacio en nombre corregido]. Ficha Melon confirmada para RADIER_INT_HA_15cm; RADIER_PULIDO_INT_HA_2cm sigue sin ficha entregada (terminacion pulida).</t>
-  </si>
-  <si>
-    <t>Perimetro real, nivel.</t>
-  </si>
-  <si>
-    <t>Coordinacion 3D del encuentro radier-muro. El modelo ya separa radier estructural y terminacion pulida.</t>
-  </si>
-  <si>
     <t>Cubiertas</t>
   </si>
   <si>
-    <t>CUBIERTA_ZINC_ONDULADO_MADERA (x1). Material renombrado de 'MT_PLACHA ONDULADA' (typo) a 'MT_PLANCHA ONDULADA ZINCALUM' (unificado con material preexistente TBC_PlanchaOnduladaZincalum). Ficha Cubiertas Nacionales confirmada (panel_ondulado_cn1020.pdf).</t>
-  </si>
-  <si>
-    <t>Pendiente (hoy sin valor), alero, nivel.</t>
-  </si>
-  <si>
-    <t>Coordinacion 3D con la estructura de madera. La pendiente sin valor indica que falta parametrizarla o declarar cubierta plana.</t>
-  </si>
-  <si>
     <t>Habitaciones</t>
   </si>
   <si>
     <t>No aplica: Rooms no tienen family type en Revit (TypeId = -1).</t>
   </si>
   <si>
-    <t>Analisis de programa espacial identifica con los primeros campos y contrasta el programa con los siguientes.</t>
-  </si>
-  <si>
-    <t>Limitación conocida: los parámetros IFC de proyecto no están vinculados a las categorías de muro cortina. Exigir información alfanumérica normalizada en montantes, paneles y rejillas requiere ampliar antes esa vinculación.</t>
-  </si>
-  <si>
-    <t>Hallazgo actualizado 08-09-2026: la familia de vigas fue renombrada de 'M_Glulam-Western Species' a 'VIGA_Pino Radiata Dimensionada_Rectangular' (resuelto). Montantes (Rectangular Mullion) y paneles (System Panel) siguen en ingles porque son familias de sistema de Revit: no se pueden renombrar (limitacion de la plataforma, no una tarea pendiente).</t>
-  </si>
-  <si>
-    <t>Empty (x192). Familia de sistema System Panel (Empty System Panel). Sin material: celosia intencional, espacio libre entre los montantes de madera (decision de proyecto confirmada). Se retiro la ficha de Vidrios Lirquen (no aplicaba).</t>
-  </si>
-  <si>
-    <t>130X130 (x16). Familia: PILAR_Pino Radiata_Rectangular. Ficha Hilam MLE confirmada sin discrepancia (glulam estructural certificado NCh2148/NCh2165). Material en el modelo: MT_PINO RADIATA (unificado el 30-09-2026).</t>
-  </si>
-  <si>
-    <t>2X8_PRINCIPAL (x8, 50x200mm) . 2X4_SECUNDARIA (x16, 50x100mm). Familia renombrada de 'M_Glulam-Western Species' a 'VIGA_Pino Radiata Dimensionada_Rectangular': CORRECCION 08-09-2026, no es glulam estructural sino madera dimensionada Arauco (MSD/Cepillado), material MT_PINO RADIATA. Discrepancia anterior resuelta.</t>
-  </si>
-  <si>
-    <t>Nombre, Numero, Nivel, Area y Perimetro completos en las 9 habitaciones (incluye PASILLO #09, Nivel NPT, 2.59 m2, agregada 08-09-2026). Departamento completo en 8 de 9 (pendiente solo en PASILLO). Todas las habitaciones estan en nivel NPT. Area total 79.45 m2.</t>
-  </si>
-  <si>
-    <t>Categorías excluidas: Ventanas, muros interiores y puertas interiores no existen en el modelo. Los vanos se resuelven con seis muros cortina y la compartimentación con dieciocho líneas de separación de habitación.</t>
-  </si>
-  <si>
     <t>Cimentación estructural</t>
   </si>
   <si>
-    <t>Nivel NOG_FUNDACIONES (cota -0.20 m), posicion bajo cada pilar, Material estructural (a nivel de instancia).</t>
-  </si>
-  <si>
-    <t>Coordinacion 3D: cada zapata debe quedar bajo su pilar. Diseno de especialidades: la dimension 60x60x50 es de anteproyecto, pendiente de calculo geotecnico y estructural.</t>
-  </si>
-  <si>
-    <t>ZAPATA_Hormigon Armado_Aislada (x16, 60x60x50cm). Familia: Zapata. Material: MT_HORMIGON ARMADO (reasignado el 30-09-2026 desde el material generico de Revit). Ficha Melon (hormigon con fibra) como referencia: la resistencia 20/25/30 MPa es un rango, no un valor unico. NDI2_Fuente_Ficha y NDI2_Observacion vinculados a esta categoria y con valores (02-10-2026).</t>
-  </si>
-  <si>
-    <t>NDI 2 como base de anteproyecto, verificado en vivo contra el modelo Revit el 06-09-2026 y actualizado el 08-09-2026 tras el renombramiento de tipos/familias y la incorporacion de fichas tecnicas de Moldupanel, Arauco y Vidrios Lirquen. Tipo = informacion fija de la familia-tipo. Instancia = informacion propia de cada elemento colocado. Actualizado el 02-10-2026: se incorporo la categoria Cimentacion estructural (16 zapatas, con parametros NDI2 vinculados), se unifico el material del pilar a MT_PINO RADIATA, se corrigieron conteos (armazon 2X4 x16) y el nivel y departamento de las habitaciones.</t>
-  </si>
-  <si>
-    <t>Nivel base y superior, longitud real del tramo. IsExternal = Si en los 17 muros (tipo e instancia, 02-10-2026); LoadBearing no esta vinculado a esta categoria.</t>
-  </si>
-  <si>
-    <t>Coordinacion 3D necesita espesor y posicion reales para el encuentro con pilares y cubierta. Diseno de especialidades usa IsExternal para separar muros de fachada de la compartimentacion.</t>
-  </si>
-  <si>
-    <t>Nivel base y superior, altura real. LoadBearing (de tipo) = 1.</t>
-  </si>
-  <si>
-    <t>Longitud real, nivel, sistema de vigas al que pertenece. LoadBearing (de tipo) = 1.</t>
+    <t>MURO_EXT_QUINCHA_12cm (×11) · M.CORTINA_EXT_CELOSIA_PINO RADIATA (FIX N) (×6). Familias: Muro básico / Muro cortina. Nivel tipo: espesor de capas y material (material real: MT_TIERRA_QUINCHA, keynote MU-01, y MT_MADERA ESTRUCTURAL, MU-02; ficha CONSTRUCCION_CON_QUINCHA_LIVIANA_1a_edicion.pdf).</t>
+  </si>
+  <si>
+    <t>Nivel base y superior (muros de quincha acoplados a la cubierta), longitud real del tramo. IsExternal = Sí en los 17 muros (tipo e instancia); LoadBearing no está vinculado a esta categoría.</t>
+  </si>
+  <si>
+    <t>Coordinación 3D necesita espesor y posición reales para el encuentro con pilares y cubierta. Diseño de especialidades usa IsExternal para separar muros de fachada de la compartimentación.</t>
+  </si>
+  <si>
+    <t>No aplica: es una línea de rejilla (CurtainGridLine), no una familia con tipo propio.</t>
+  </si>
+  <si>
+    <t>Modulación U/V, posición en el muro, muro anfitrión.</t>
+  </si>
+  <si>
+    <t>Revisión del diseño: la modulación 2×16 (1 línea U, 15 líneas V) es una decisión de proyecto. Coordinación 3D: gobierna dónde caen montantes y paneles.</t>
+  </si>
+  <si>
+    <t>12.5x100mm_PINO RADIATA (×396). Familia de sistema: Rectangular Mullion (nombre de sistema Revit, no renombrable). Material: MT_PINO RADIATA (keynote MA-01). Ficha: Arauco Cepillado.</t>
+  </si>
+  <si>
+    <t>Longitud real, posición en la rejilla, resolución en esquinas.</t>
+  </si>
+  <si>
+    <t>Coordinación 3D: el montante perimetral choca con viga y pilar. Diseño de especialidades: es madera vista, su sección forma parte del partido.</t>
+  </si>
+  <si>
+    <t>Empty (×192). Familia de sistema Empty System Panel. Sin material: celosía intencional, espacio libre entre los montantes de madera (decisión de proyecto confirmada). No lleva keynote.</t>
+  </si>
+  <si>
+    <t>Dimensión real del paño, posición en la rejilla.</t>
+  </si>
+  <si>
+    <t>Revisión del diseño: el vacío entre montantes condiciona luz, vista y ventilación; verificar si requiere hoja operable.</t>
+  </si>
+  <si>
+    <t>80x210cm (×2). Familia: PRT_Puerta_INT_Simple_1 Panel_PINO RADIATA. Material: MT_PINO RADIATA PUERTA (keynote PU-01; antes TBC_Madera). Ficha: Moldupanel, Puerta Pino Radiata Italia. La familia declara además MT_ALUMINIO GRAFITO y MT_GENERICO PUERTA sin geometría; los herrajes no están modelados (proveedor de referencia: Häfele, vía El Carpintero).</t>
+  </si>
+  <si>
+    <t>Muro anfitrión, sentido de apertura, Marca (6, 9), IsExternal.</t>
+  </si>
+  <si>
+    <t>Revisión del diseño verifica ancho libre y sentido de apertura. IsExternal distinguiría acceso de interior.</t>
+  </si>
+  <si>
+    <t>130X130 (×16). Familia: PILAR_Pino Radiata_Rectangular. Ficha Hilam MLE como referencia de producto (glulam estructural certificado NCh2148/NCh2165). Material en el modelo: MT_PINO RADIATA (unificado el 30-09-2026; keynote MA-01).</t>
+  </si>
+  <si>
+    <t>Nivel base y superior (parte superior acoplada a la cubierta), altura real. LoadBearing (de tipo) = 1.</t>
+  </si>
+  <si>
+    <t>Coordinación 3D: el pilar choca con muros y vigas. La sección debe ser dato del tipo, no solo su nombre.</t>
+  </si>
+  <si>
+    <t>2"X8" Sin cepillar (×16, 50×200 mm) · 2"X4" Cepillada (×16, 50×100 mm). Familia VIGA_PINO RADIATA_Rectangular (renombrada de VIGA_Pino Radiata Dimensionada_Rectangular, y antes de M_Glulam-Western Species): madera dimensionada Arauco (MSD / Cepillado), no glulam. Material MT_PINO RADIATA (keynote MA-01).</t>
+  </si>
+  <si>
+    <t>Longitud real, nivel, sistema de vigas al que pertenece (15 sistemas); extremos ajustados a la cara inferior de la cubierta. LoadBearing (de tipo) = 1 en ambos tipos.</t>
+  </si>
+  <si>
+    <t>Revisión del diseño comprueba la jerarquía entre vigas principales y secundarias, ya resuelta en los tipos.</t>
+  </si>
+  <si>
+    <t>FUNDACIÓN AISLADA_HA_60x60x50cm (×16). Familia FUNDACIÓN AISLADA (antes Zapata). Material: MT_HORMIGON ARMADO (RA-01; reasignado el 30-09-2026 desde el material genérico de Revit). Ficha Melón (hormigón con fibra) como referencia: la resistencia 20/25/30 MPa es un rango, no un valor único. NDI2_Fuente_Ficha y NDI2_Observacion vinculados a esta categoría y con valores.</t>
+  </si>
+  <si>
+    <t>Nivel NOG_FUNDACIONES (cota −0,20 m), posición bajo cada pilar, Material estructural (a nivel de instancia).</t>
+  </si>
+  <si>
+    <t>Coordinación 3D: cada zapata debe quedar bajo su pilar. Diseño de especialidades: la dimensión 60x60x50 es de anteproyecto, pendiente de cálculo geotécnico y estructural.</t>
+  </si>
+  <si>
+    <t>RADIER_INT_HA_15cm (×1; MT_HORMIGON ARMADO, RA-01) · PAV_INT_HORMIGON PULIDO_2cm (×1; MT_HORMIGON PULIDO, RA-02; antes RADIER_PULIDO_INT_HA_2cm). Ficha Melón confirmada para el radier; Sikafloor-3 QuartzTop (Sika Chile) para la terminación pulida.</t>
+  </si>
+  <si>
+    <t>Perímetro real, nivel.</t>
+  </si>
+  <si>
+    <t>Coordinación 3D del encuentro radier-muro. El modelo ya separa radier estructural y terminación pulida.</t>
+  </si>
+  <si>
+    <t>CUBIERTA_ZINC ONDULADO_10cm (×4 faldones; antes CUBIERTA_ZINC_ONDULADO_MADERA). Material MT_PLANCHA ONDULADA ZINCALUM (CU-01) sobre capa estructural MT_PINO RADIATA. Ficha Cubiertas Nacionales confirmada (panel_ondulado_cn1020.pdf).</t>
+  </si>
+  <si>
+    <t>Pendiente 1,7 % (4 faldones que bajan hacia el patio central), alero, nivel CUBIERTA (+2,50 m). IsExternal = Sí.</t>
+  </si>
+  <si>
+    <t>Coordinación 3D con la estructura de madera: pilares, muros de quincha y vigas se ajustan a la cara inferior de la cubierta.</t>
+  </si>
+  <si>
+    <t>Nombre, Número, Nivel, Área y Perímetro completos en las 9 habitaciones (incluye PASILLO #09, Nivel NPT, 2,60 m²). Departamento completo en 8 de 9 (pendiente solo en PASILLO). Todas las habitaciones están en nivel NPT. Área total 79,45 m².</t>
+  </si>
+  <si>
+    <t>Análisis de programa espacial identifica con los primeros campos y contrasta el programa con los siguientes.</t>
+  </si>
+  <si>
+    <t>Aparatos sanitarios</t>
+  </si>
+  <si>
+    <t>PLM_WC_ceramica_New Valencia a muro: 41x69cm (×2) · PLM_Lavamanos_ceramica_Ciro pedestal: 53x41cm (×2) · PLM_Bebedero_acero inoxidable_Wolfen sensor pie: 31x32cm (×3). Materiales con keynote: MT_LOZA INODORO (SA-01), MT_LOZA LAVAMANOS (SA-02), MT_METAL CROMADO (SA-03), MT_ACERO INOXIDABLE CEPILLADO y MT_LATON CROMADO (SA-04). Fichas: Fanaloza (Catalogo-Ferretero_2025.pdf) y Reece Wolfen WDF2SS, cód. 1308142.</t>
+  </si>
+  <si>
+    <t>Recinto y nivel, muro anfitrión del WC (a muro), consumo de agua del WC (4,1 / 6 L).</t>
+  </si>
+  <si>
+    <t>Estimación de cantidades: conteo de artefactos. Validación normativa: instalación sanitaria (RIDAA, sección 00 de la EETT). Coordinación 3D con muros y trazados.</t>
+  </si>
+  <si>
+    <t>Mobiliario</t>
+  </si>
+  <si>
+    <t>MBL_Mueble base cocina_Lavaplatos: 80x60cm (×1) · MBL_Mueble base cocina_Melamina: 104x64cm (×2). Material con keynote: MT_ACERO INOXIDABLE (MO-01). Referencia de lavaplatos: catálogo Fanaloza 2025 (EETT sec. 07).</t>
+  </si>
+  <si>
+    <t>Recinto, nivel, posición en la zona de apoyo.</t>
+  </si>
+  <si>
+    <t>Análisis de programa espacial: equipamiento de la zona de apoyo. Estimación de cantidades: conteo de muebles.</t>
+  </si>
+  <si>
+    <t>Emplazamiento</t>
+  </si>
+  <si>
+    <t>SITIO_Banca_acero galvanizado y madera: 250x50cm (×5) · SITIO_Bicicletero_acero galvanizado_U: 2 bicicletas (×5). Materiales con keynote: MT_BANCA PATAS y MT_BANCA ASIENTO (EQ-02), MT_ACERO GALVANIZADO (EQ-01). Referencias: Metalco Big Harris y Dero U-Lockit (EETT sec. 07).</t>
+  </si>
+  <si>
+    <t>Posición, recinto o exterior, orientación.</t>
+  </si>
+  <si>
+    <t>Análisis de programa espacial: capacidad de estacionamiento (5 módulos de 2 bicicletas) y descanso exterior. Estimación de cantidades.</t>
+  </si>
+  <si>
+    <t>NDI 2 como base de anteproyecto, verificado en vivo contra el modelo Revit el 20-10-2026. Tipo = información fija de la familia-tipo. Instancia = información propia de cada elemento colocado. Actualizado el 20-10-2026: familias, tipos y materiales renombrados según el protocolo de nombres DIPBIM; keynotes de material AA-NN ligados a la EETT (sec. 01 a 07); vigas, pilares y muros de quincha ajustados a la cara inferior de la cubierta de 4 faldones (pendiente 1,7 %); se incorporaron las categorías Aparatos sanitarios, Mobiliario y Emplazamiento, ya modeladas.</t>
+  </si>
+  <si>
+    <t>Categorías excluidas: Ventanas, muros interiores y puertas interiores no existen en el modelo. Los vanos se resuelven con seis muros cortina y la compartimentación con dieciocho líneas de separación de habitación. Vegetación (1 árbol VEG_DWG_Arbol 4m) y los elementos 2D de la plantilla no se incluyen en la tabla.</t>
+  </si>
+  <si>
+    <t>Limitación conocida: los parámetros IFC de proyecto no están vinculados a las categorías de muro cortina. Exigir información alfanumérica normalizada en montantes, paneles y rejillas requiere ampliar antes esa vinculación. Los parámetros NDI2 tampoco están vinculados aún a Aparatos sanitarios, Mobiliario y Emplazamiento.</t>
+  </si>
+  <si>
+    <t>Hallazgo actualizado 20-10-2026: familias y tipos renombrados según el protocolo de nombres DIPBIM. Montantes (Rectangular Mullion) y paneles (Empty System Panel) siguen con nombre de sistema Revit en inglés porque son familias de sistema: no se pueden renombrar (limitación de la plataforma, no una tarea pendiente).</t>
   </si>
 </sst>
 </file>
@@ -544,31 +580,31 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -807,7 +843,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
@@ -817,7 +853,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16"/>
@@ -826,7 +862,7 @@
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="16"/>
@@ -835,7 +871,7 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="16"/>
@@ -851,7 +887,7 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="21" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="16"/>
@@ -860,69 +896,69 @@
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="21" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="19"/>
+      <c r="D6" s="18"/>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="21" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="19"/>
+      <c r="D7" s="18"/>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="21" t="s">
+      <c r="B8" s="18"/>
+      <c r="C8" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="19"/>
+      <c r="D8" s="18"/>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="21" t="s">
+      <c r="B9" s="18"/>
+      <c r="C9" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="19"/>
+      <c r="D9" s="18"/>
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="21" t="s">
+      <c r="B10" s="18"/>
+      <c r="C10" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="19"/>
+      <c r="D10" s="18"/>
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="21" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="19"/>
+      <c r="D11" s="18"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1037,7 +1073,7 @@
       <c r="E20" s="1"/>
     </row>
     <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="25" t="s">
         <v>40</v>
       </c>
       <c r="B21" s="16"/>
@@ -1045,9 +1081,9 @@
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
     </row>
-    <row r="22" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
-        <v>89</v>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
+        <v>102</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -1071,7 +1107,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="102" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>2</v>
       </c>
@@ -1079,115 +1115,115 @@
         <v>46</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>2</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>2</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>2</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="102" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>2</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>2</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="102" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>2</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="114.75" x14ac:dyDescent="0.25">
@@ -1195,98 +1231,158 @@
         <v>2</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>2</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>2</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>2</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-    </row>
-    <row r="38" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-    </row>
-    <row r="39" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="127.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="11">
+        <v>2</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="11">
+        <v>2</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A38" s="11">
+        <v>2</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+    </row>
+    <row r="41" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+    </row>
+    <row r="42" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="A8:B8"/>
@@ -1299,17 +1395,8 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A37:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="36" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="25" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/03_Documentos_Tecnicos/PEB_Pausa_Maule_completado.xlsx
+++ b/03_Documentos_Tecnicos/PEB_Pausa_Maule_completado.xlsx
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>CUBIERTA_ZINC ONDULADO_10cm (×4 faldones; antes CUBIERTA_ZINC_ONDULADO_MADERA). Material MT_PLANCHA ONDULADA ZINCALUM (CU-01) en capa única de 18 mm sobre el armazón. Ficha Cubiertas Nacionales confirmada (panel_ondulado_cn1020.pdf).</t>
+          <t>CUBIERTA_ZINC ONDULADO_18mm (×4 faldones; antes CUBIERTA_ZINC_ONDULADO_MADERA). Material MT_PLANCHA ONDULADA ZINCALUM (CU-01) en capa única de 18 mm sobre el armazón. Ficha Cubiertas Nacionales confirmada (panel_ondulado_cn1020.pdf).</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
